--- a/Data/EC/NIT-9008602191.xlsx
+++ b/Data/EC/NIT-9008602191.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Documents\NIYARAKY\MACROS AJUSTADAS\2- MACRO COMFENALCO CARTAGENA ACTUALIZACION\Estados De Cuenta\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ysarm\OneDrive\Desktop\MACROS\2- MACRO COMFENALCO CARTAGENA ACTUALIZACION\Estados De Cuenta\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4F20E9C4-F03F-46D3-8464-C79F7DAE991F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{FCDF8C4B-70E9-4CDF-9EDB-80999526F44A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{B0DCBFC3-0F24-429E-81E2-0EFFEA3BFE8D}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{5938663D-CEA0-4D5D-9A85-ECDD61C6A2DD}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="53">
   <si>
     <t>Tipo Doc Trabajador</t>
   </si>
@@ -71,79 +71,97 @@
     <t>LISMAR VANESSA MIJARES RIOS</t>
   </si>
   <si>
+    <t>2602</t>
+  </si>
+  <si>
+    <t>2601</t>
+  </si>
+  <si>
+    <t>2512</t>
+  </si>
+  <si>
+    <t>2511</t>
+  </si>
+  <si>
+    <t>2510</t>
+  </si>
+  <si>
+    <t>2509</t>
+  </si>
+  <si>
+    <t>2508</t>
+  </si>
+  <si>
+    <t>2507</t>
+  </si>
+  <si>
+    <t>2506</t>
+  </si>
+  <si>
+    <t>2505</t>
+  </si>
+  <si>
+    <t>2504</t>
+  </si>
+  <si>
+    <t>2503</t>
+  </si>
+  <si>
+    <t>2502</t>
+  </si>
+  <si>
+    <t>2501</t>
+  </si>
+  <si>
+    <t>2412</t>
+  </si>
+  <si>
+    <t>2411</t>
+  </si>
+  <si>
+    <t>2410</t>
+  </si>
+  <si>
+    <t>2409</t>
+  </si>
+  <si>
+    <t>2408</t>
+  </si>
+  <si>
+    <t>2407</t>
+  </si>
+  <si>
+    <t>2406</t>
+  </si>
+  <si>
+    <t>2405</t>
+  </si>
+  <si>
+    <t>2404</t>
+  </si>
+  <si>
+    <t>2403</t>
+  </si>
+  <si>
+    <t>2402</t>
+  </si>
+  <si>
+    <t>2401</t>
+  </si>
+  <si>
+    <t>2312</t>
+  </si>
+  <si>
+    <t>2311</t>
+  </si>
+  <si>
+    <t>2310</t>
+  </si>
+  <si>
+    <t>2309</t>
+  </si>
+  <si>
     <t>2308</t>
-  </si>
-  <si>
-    <t>2309</t>
-  </si>
-  <si>
-    <t>2310</t>
-  </si>
-  <si>
-    <t>2311</t>
-  </si>
-  <si>
-    <t>2312</t>
-  </si>
-  <si>
-    <t>2401</t>
-  </si>
-  <si>
-    <t>2402</t>
-  </si>
-  <si>
-    <t>2403</t>
-  </si>
-  <si>
-    <t>2404</t>
-  </si>
-  <si>
-    <t>2405</t>
-  </si>
-  <si>
-    <t>2406</t>
-  </si>
-  <si>
-    <t>2407</t>
-  </si>
-  <si>
-    <t>2408</t>
-  </si>
-  <si>
-    <t>2409</t>
-  </si>
-  <si>
-    <t>2410</t>
-  </si>
-  <si>
-    <t>2411</t>
-  </si>
-  <si>
-    <t>2412</t>
-  </si>
-  <si>
-    <t>2501</t>
-  </si>
-  <si>
-    <t>2502</t>
-  </si>
-  <si>
-    <t>2503</t>
-  </si>
-  <si>
-    <t>2504</t>
-  </si>
-  <si>
-    <t>2505</t>
-  </si>
-  <si>
-    <t>2506</t>
-  </si>
-  <si>
-    <t>2507</t>
-  </si>
-  <si>
-    <t>2508</t>
   </si>
   <si>
     <t>ESTADO DE CUENTA</t>
@@ -242,9 +260,7 @@
       <left style="thin">
         <color indexed="64"/>
       </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
+      <right/>
       <top style="thin">
         <color indexed="64"/>
       </top>
@@ -257,7 +273,9 @@
       <left style="thin">
         <color indexed="64"/>
       </left>
-      <right/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
       <top style="thin">
         <color indexed="64"/>
       </top>
@@ -457,23 +475,23 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -501,10 +519,10 @@
     <xf numFmtId="164" fontId="2" fillId="0" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -542,22 +560,22 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>674250</xdr:colOff>
+      <xdr:colOff>717113</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>62300</xdr:rowOff>
+      <xdr:rowOff>75000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>437000</xdr:colOff>
+      <xdr:colOff>435413</xdr:colOff>
       <xdr:row>4</xdr:row>
-      <xdr:rowOff>121850</xdr:rowOff>
+      <xdr:rowOff>115500</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="3" name="Imagen 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3BCAE926-B9B8-9A82-F0B6-974CDC9D6E4D}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2FD53057-5E35-BB93-FCC4-32DBDF4A1792}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -579,7 +597,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="928250" y="246450"/>
+          <a:off x="964763" y="265500"/>
           <a:ext cx="975600" cy="612000"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -908,27 +926,27 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0C425F9B-B15C-4438-8407-28D7FAA950F4}">
-  <dimension ref="B2:J46"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B030CFE6-2EED-489B-9008-28BBAA3FEFCF}">
+  <dimension ref="B2:J52"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="3.6328125" customWidth="1"/>
-    <col min="2" max="2" width="18.54296875" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.7265625" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="30" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.54296875" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.1796875" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.36328125" style="2" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="19.36328125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="18.08984375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3.7109375" customWidth="1"/>
+    <col min="2" max="2" width="19.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="31.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="19.140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="2" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B2" s="3"/>
       <c r="C2" s="28"/>
       <c r="D2" s="29" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="E2" s="29"/>
       <c r="F2" s="29"/>
@@ -937,7 +955,7 @@
       <c r="I2" s="29"/>
       <c r="J2" s="29"/>
     </row>
-    <row r="3" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B3" s="3"/>
       <c r="C3" s="28"/>
       <c r="D3" s="30"/>
@@ -948,7 +966,7 @@
       <c r="I3" s="30"/>
       <c r="J3" s="30"/>
     </row>
-    <row r="4" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B4" s="3"/>
       <c r="C4" s="28"/>
       <c r="D4" s="30"/>
@@ -959,7 +977,7 @@
       <c r="I4" s="30"/>
       <c r="J4" s="30"/>
     </row>
-    <row r="5" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B5" s="3"/>
       <c r="C5" s="28"/>
       <c r="D5" s="31"/>
@@ -970,10 +988,10 @@
       <c r="I5" s="31"/>
       <c r="J5" s="31"/>
     </row>
-    <row r="6" spans="2:10" ht="9" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="7" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:10" ht="9" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="7" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B7" s="4" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="C7" s="4"/>
       <c r="D7" s="27"/>
@@ -986,8 +1004,8 @@
       <c r="I7" s="6"/>
       <c r="J7" s="6"/>
     </row>
-    <row r="8" spans="2:10" ht="7.5" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="9" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:10" ht="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="9" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B9" s="4" t="s">
         <v>6</v>
       </c>
@@ -1002,15 +1020,15 @@
       <c r="I9" s="6"/>
       <c r="J9" s="6"/>
     </row>
-    <row r="10" spans="2:10" ht="6.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="11" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:10" ht="6.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="11" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B11" s="4" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="C11" s="4"/>
       <c r="D11" s="27"/>
       <c r="E11" s="7">
-        <v>1228525</v>
+        <v>1523371</v>
       </c>
       <c r="F11" s="7"/>
       <c r="G11" s="7"/>
@@ -1018,27 +1036,27 @@
       <c r="I11" s="7"/>
       <c r="J11" s="7"/>
     </row>
-    <row r="12" spans="2:10" ht="4.5" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="13" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:10" ht="4.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="13" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B13" s="9" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="C13" s="5">
         <v>1</v>
       </c>
       <c r="D13" s="5"/>
       <c r="E13" s="8" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="F13" s="5">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="G13" s="5"/>
       <c r="H13" s="5"/>
       <c r="I13" s="5"/>
       <c r="J13" s="5"/>
     </row>
-    <row r="15" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="15" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B15" s="10" t="s">
         <v>0</v>
       </c>
@@ -1058,16 +1076,16 @@
         <v>5</v>
       </c>
       <c r="H15" s="13" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="I15" s="13" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="J15" s="14" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="16" spans="2:10" x14ac:dyDescent="0.35">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="16" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B16" s="15" t="s">
         <v>8</v>
       </c>
@@ -1090,7 +1108,7 @@
       <c r="I16" s="19"/>
       <c r="J16" s="20"/>
     </row>
-    <row r="17" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B17" s="15" t="s">
         <v>8</v>
       </c>
@@ -1113,7 +1131,7 @@
       <c r="I17" s="19"/>
       <c r="J17" s="20"/>
     </row>
-    <row r="18" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B18" s="15" t="s">
         <v>8</v>
       </c>
@@ -1136,7 +1154,7 @@
       <c r="I18" s="19"/>
       <c r="J18" s="20"/>
     </row>
-    <row r="19" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B19" s="15" t="s">
         <v>8</v>
       </c>
@@ -1159,7 +1177,7 @@
       <c r="I19" s="19"/>
       <c r="J19" s="20"/>
     </row>
-    <row r="20" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B20" s="15" t="s">
         <v>8</v>
       </c>
@@ -1182,7 +1200,7 @@
       <c r="I20" s="19"/>
       <c r="J20" s="20"/>
     </row>
-    <row r="21" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B21" s="15" t="s">
         <v>8</v>
       </c>
@@ -1205,7 +1223,7 @@
       <c r="I21" s="19"/>
       <c r="J21" s="20"/>
     </row>
-    <row r="22" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B22" s="15" t="s">
         <v>8</v>
       </c>
@@ -1228,7 +1246,7 @@
       <c r="I22" s="19"/>
       <c r="J22" s="20"/>
     </row>
-    <row r="23" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B23" s="15" t="s">
         <v>8</v>
       </c>
@@ -1251,7 +1269,7 @@
       <c r="I23" s="19"/>
       <c r="J23" s="20"/>
     </row>
-    <row r="24" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B24" s="15" t="s">
         <v>8</v>
       </c>
@@ -1274,7 +1292,7 @@
       <c r="I24" s="19"/>
       <c r="J24" s="20"/>
     </row>
-    <row r="25" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="25" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B25" s="15" t="s">
         <v>8</v>
       </c>
@@ -1297,7 +1315,7 @@
       <c r="I25" s="19"/>
       <c r="J25" s="20"/>
     </row>
-    <row r="26" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="26" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B26" s="15" t="s">
         <v>8</v>
       </c>
@@ -1320,7 +1338,7 @@
       <c r="I26" s="19"/>
       <c r="J26" s="20"/>
     </row>
-    <row r="27" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="27" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B27" s="15" t="s">
         <v>8</v>
       </c>
@@ -1343,7 +1361,7 @@
       <c r="I27" s="19"/>
       <c r="J27" s="20"/>
     </row>
-    <row r="28" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="28" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B28" s="15" t="s">
         <v>8</v>
       </c>
@@ -1366,7 +1384,7 @@
       <c r="I28" s="19"/>
       <c r="J28" s="20"/>
     </row>
-    <row r="29" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="29" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B29" s="15" t="s">
         <v>8</v>
       </c>
@@ -1389,7 +1407,7 @@
       <c r="I29" s="19"/>
       <c r="J29" s="20"/>
     </row>
-    <row r="30" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="30" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B30" s="15" t="s">
         <v>8</v>
       </c>
@@ -1412,7 +1430,7 @@
       <c r="I30" s="19"/>
       <c r="J30" s="20"/>
     </row>
-    <row r="31" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="31" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B31" s="15" t="s">
         <v>8</v>
       </c>
@@ -1435,7 +1453,7 @@
       <c r="I31" s="19"/>
       <c r="J31" s="20"/>
     </row>
-    <row r="32" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="32" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B32" s="15" t="s">
         <v>8</v>
       </c>
@@ -1458,7 +1476,7 @@
       <c r="I32" s="19"/>
       <c r="J32" s="20"/>
     </row>
-    <row r="33" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="33" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B33" s="15" t="s">
         <v>8</v>
       </c>
@@ -1481,7 +1499,7 @@
       <c r="I33" s="19"/>
       <c r="J33" s="20"/>
     </row>
-    <row r="34" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="34" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B34" s="15" t="s">
         <v>8</v>
       </c>
@@ -1504,7 +1522,7 @@
       <c r="I34" s="19"/>
       <c r="J34" s="20"/>
     </row>
-    <row r="35" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="35" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B35" s="15" t="s">
         <v>8</v>
       </c>
@@ -1527,7 +1545,7 @@
       <c r="I35" s="19"/>
       <c r="J35" s="20"/>
     </row>
-    <row r="36" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="36" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B36" s="15" t="s">
         <v>8</v>
       </c>
@@ -1550,7 +1568,7 @@
       <c r="I36" s="19"/>
       <c r="J36" s="20"/>
     </row>
-    <row r="37" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="37" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B37" s="15" t="s">
         <v>8</v>
       </c>
@@ -1573,7 +1591,7 @@
       <c r="I37" s="19"/>
       <c r="J37" s="20"/>
     </row>
-    <row r="38" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="38" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B38" s="15" t="s">
         <v>8</v>
       </c>
@@ -1596,7 +1614,7 @@
       <c r="I38" s="19"/>
       <c r="J38" s="20"/>
     </row>
-    <row r="39" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="39" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B39" s="15" t="s">
         <v>8</v>
       </c>
@@ -1619,57 +1637,195 @@
       <c r="I39" s="19"/>
       <c r="J39" s="20"/>
     </row>
-    <row r="40" spans="2:10" x14ac:dyDescent="0.35">
-      <c r="B40" s="21" t="s">
-        <v>8</v>
-      </c>
-      <c r="C40" s="22" t="s">
-        <v>9</v>
-      </c>
-      <c r="D40" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="E40" s="22" t="s">
+    <row r="40" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B40" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="C40" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="D40" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="E40" s="16" t="s">
         <v>35</v>
       </c>
-      <c r="F40" s="24">
-        <v>49141</v>
-      </c>
-      <c r="G40" s="24">
-        <v>1228526</v>
-      </c>
-      <c r="H40" s="25"/>
-      <c r="I40" s="25"/>
-      <c r="J40" s="26"/>
-    </row>
-    <row r="45" spans="2:10" x14ac:dyDescent="0.35">
-      <c r="B45" s="32" t="s">
-        <v>45</v>
-      </c>
-      <c r="C45" s="32"/>
-      <c r="H45" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="I45" s="1"/>
-      <c r="J45" s="1"/>
-    </row>
-    <row r="46" spans="2:10" x14ac:dyDescent="0.35">
-      <c r="B46" s="32" t="s">
-        <v>44</v>
-      </c>
-      <c r="C46" s="32"/>
-      <c r="H46" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="I46" s="1"/>
-      <c r="J46" s="1"/>
+      <c r="F40" s="18">
+        <v>49141</v>
+      </c>
+      <c r="G40" s="18">
+        <v>1228526</v>
+      </c>
+      <c r="H40" s="19"/>
+      <c r="I40" s="19"/>
+      <c r="J40" s="20"/>
+    </row>
+    <row r="41" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B41" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="C41" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="D41" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="E41" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="F41" s="18">
+        <v>49141</v>
+      </c>
+      <c r="G41" s="18">
+        <v>1228526</v>
+      </c>
+      <c r="H41" s="19"/>
+      <c r="I41" s="19"/>
+      <c r="J41" s="20"/>
+    </row>
+    <row r="42" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B42" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="C42" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="D42" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="E42" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="F42" s="18">
+        <v>49141</v>
+      </c>
+      <c r="G42" s="18">
+        <v>1228526</v>
+      </c>
+      <c r="H42" s="19"/>
+      <c r="I42" s="19"/>
+      <c r="J42" s="20"/>
+    </row>
+    <row r="43" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B43" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="C43" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="D43" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="E43" s="16" t="s">
+        <v>38</v>
+      </c>
+      <c r="F43" s="18">
+        <v>49141</v>
+      </c>
+      <c r="G43" s="18">
+        <v>1228526</v>
+      </c>
+      <c r="H43" s="19"/>
+      <c r="I43" s="19"/>
+      <c r="J43" s="20"/>
+    </row>
+    <row r="44" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B44" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="C44" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="D44" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="E44" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="F44" s="18">
+        <v>49141</v>
+      </c>
+      <c r="G44" s="18">
+        <v>1228526</v>
+      </c>
+      <c r="H44" s="19"/>
+      <c r="I44" s="19"/>
+      <c r="J44" s="20"/>
+    </row>
+    <row r="45" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B45" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="C45" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="D45" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="E45" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="F45" s="18">
+        <v>49141</v>
+      </c>
+      <c r="G45" s="18">
+        <v>1228526</v>
+      </c>
+      <c r="H45" s="19"/>
+      <c r="I45" s="19"/>
+      <c r="J45" s="20"/>
+    </row>
+    <row r="46" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B46" s="21" t="s">
+        <v>8</v>
+      </c>
+      <c r="C46" s="22" t="s">
+        <v>9</v>
+      </c>
+      <c r="D46" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="E46" s="22" t="s">
+        <v>41</v>
+      </c>
+      <c r="F46" s="24">
+        <v>49141</v>
+      </c>
+      <c r="G46" s="24">
+        <v>1228526</v>
+      </c>
+      <c r="H46" s="25"/>
+      <c r="I46" s="25"/>
+      <c r="J46" s="26"/>
+    </row>
+    <row r="51" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B51" s="32" t="s">
+        <v>51</v>
+      </c>
+      <c r="C51" s="32"/>
+      <c r="H51" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="I51" s="1"/>
+      <c r="J51" s="1"/>
+    </row>
+    <row r="52" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B52" s="32" t="s">
+        <v>50</v>
+      </c>
+      <c r="C52" s="32"/>
+      <c r="H52" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="I52" s="1"/>
+      <c r="J52" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B45:C45"/>
-    <mergeCell ref="H46:J46"/>
-    <mergeCell ref="H45:J45"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="B51:C51"/>
+    <mergeCell ref="H52:J52"/>
+    <mergeCell ref="H51:J51"/>
     <mergeCell ref="B11:D11"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="D2:J5"/>
